--- a/ROSALES/Agosto/expensas rosales Agostoxlsx.xlsx
+++ b/ROSALES/Agosto/expensas rosales Agostoxlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D8DB37-CE23-4574-B4AA-73AB57F19CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C380288-15FE-409B-85FC-3F1AC4739E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="139">
   <si>
     <t>TOTAL</t>
   </si>
@@ -410,38 +410,41 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Vto. 14/08</t>
-  </si>
-  <si>
-    <t>LIQUIDACIÓN EXPENSAS JULIO 2025</t>
-  </si>
-  <si>
-    <t>Fumigacion mes de JULIO</t>
-  </si>
-  <si>
-    <t>EGRESOS DEL MES DE JULIO</t>
-  </si>
-  <si>
     <t>Ascensores Lema - Provision y colocacion de Coliza</t>
   </si>
   <si>
     <t>Subidos en JULI 2025</t>
-  </si>
-  <si>
-    <t>TSG MES 4</t>
-  </si>
-  <si>
-    <t>TSG MES 5</t>
-  </si>
-  <si>
-    <t>TSG MES 6</t>
-  </si>
-  <si>
-    <t>TSG MES 7</t>
   </si>
   <si>
     <t xml:space="preserve">CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES
 </t>
+  </si>
+  <si>
+    <t>Vto. 15/09</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS AGOSTO 2025</t>
+  </si>
+  <si>
+    <t>Fumigacion mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>EGRESOS DEL MES DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TSG MES 8</t>
+  </si>
+  <si>
+    <t>Leonardo rosales limpieza</t>
+  </si>
+  <si>
+    <t>ARBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roxi </t>
+  </si>
+  <si>
+    <t>Carina</t>
   </si>
 </sst>
 </file>
@@ -449,19 +452,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="13">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="172" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="34" x14ac:knownFonts="1">
     <font>
@@ -1150,11 +1153,11 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1162,7 +1165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1171,27 +1174,27 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1204,8 +1207,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1213,18 +1216,18 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1233,8 +1236,8 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1253,7 +1256,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1264,28 +1267,28 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1300,13 +1303,13 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1317,24 +1320,24 @@
     <xf numFmtId="43" fontId="26" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1344,7 +1347,7 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="27" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1359,19 +1362,19 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="28" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="28" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="25" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1385,37 +1388,37 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="28" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="28" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1425,10 +1428,10 @@
     <xf numFmtId="43" fontId="26" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="25" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="25" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="25" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1437,8 +1440,8 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1447,9 +1450,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1457,11 +1460,11 @@
     <xf numFmtId="43" fontId="26" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="28" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="25" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="28" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1469,10 +1472,10 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="26" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1480,9 +1483,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -1496,13 +1499,19 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1513,15 +1522,14 @@
     <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1934,17 +1942,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:F68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1952,101 +1960,101 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>124</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="33">
+      <c r="C18" s="231">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="218">
-        <v>350140.35</v>
+      <c r="C19" s="232">
+        <v>321313.76</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B20" s="39"/>
       <c r="C20" s="218">
@@ -2055,376 +2063,387 @@
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="28" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="33">
-        <v>65000</v>
+      <c r="C21" s="232">
+        <v>571077.30000000005</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="28" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="B22" s="39"/>
-      <c r="C22" s="33">
-        <v>15181</v>
+      <c r="C22" s="231">
+        <v>77800</v>
       </c>
       <c r="D22" s="20"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="28" t="s">
         <v>134</v>
       </c>
       <c r="B23" s="39"/>
-      <c r="C23" s="33">
-        <v>15181</v>
+      <c r="C23" s="231">
+        <v>14856</v>
       </c>
       <c r="D23" s="20"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="B24" s="39"/>
+        <v>11</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>23</v>
+      </c>
       <c r="C24" s="33">
-        <v>14134</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="33">
-        <v>14856</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="33">
         <v>83400</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="6"/>
-      <c r="F26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="40"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="23">
-        <f>SUM(C17:C26)</f>
-        <v>914546.35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="35" t="s">
+      <c r="D24" s="4"/>
+      <c r="E24" s="6"/>
+      <c r="F24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="40"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="23">
+        <f>SUM(C17:C24)</f>
+        <v>1425101.06</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="211"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="B26" s="39"/>
+      <c r="C26" s="211"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="33">
+      <c r="B27" s="42"/>
+      <c r="C27" s="33">
         <f>349151.87+ (349151.87*10%)</f>
         <v>384067.05699999997</v>
       </c>
+      <c r="D27" s="45"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="231">
+        <v>5684</v>
+      </c>
+      <c r="D28" s="45"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="233" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="140"/>
+      <c r="C29" s="231">
+        <v>400000</v>
+      </c>
       <c r="D29" s="45"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="33">
-        <v>5684</v>
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="207" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="140"/>
+      <c r="C30" s="231">
+        <v>49940</v>
       </c>
       <c r="D30" s="45"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="207" t="s">
-        <v>126</v>
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="233" t="s">
+        <v>137</v>
       </c>
       <c r="B31" s="140"/>
-      <c r="C31" s="33">
-        <v>52800</v>
+      <c r="C31" s="231">
+        <v>115000</v>
       </c>
       <c r="D31" s="45"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="33">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="233" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" s="140"/>
+      <c r="C32" s="231">
+        <v>88650</v>
+      </c>
+      <c r="D32" s="45"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="42"/>
+      <c r="C33" s="33">
         <v>45000</v>
       </c>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="40"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="23">
-        <f>SUM(C28:C33)</f>
-        <v>487551.05699999997</v>
-      </c>
+      <c r="B34" s="39"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="6"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="30" t="s">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="40"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="23">
+        <f>SUM(C26:C34)</f>
+        <v>1088341.057</v>
+      </c>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="43">
-        <f>+C34+C27</f>
-        <v>1402097.4069999999</v>
-      </c>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C36" s="24"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="43">
+        <f>+C35+C25</f>
+        <v>2513442.1170000001</v>
+      </c>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>18</v>
-      </c>
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C37" s="24"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="33"/>
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="24"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="28"/>
       <c r="B39" s="28"/>
-      <c r="C39" s="34"/>
+      <c r="C39" s="33"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="28"/>
       <c r="B40" s="28"/>
       <c r="C40" s="34"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C41" s="25"/>
+    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="28"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="34"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="212" t="s">
+    <row r="42" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C42" s="25"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="212" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="212"/>
-      <c r="C42" s="213">
+      <c r="B43" s="212"/>
+      <c r="C43" s="213">
         <v>1000000</v>
       </c>
-      <c r="F42" s="12"/>
-    </row>
-    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C43" s="25"/>
       <c r="F43" s="12"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
+    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C44" s="25"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14">
-        <f>+C38+C39+C40+C43</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="6"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
+      <c r="B45" s="13"/>
+      <c r="C45" s="14">
+        <f>+C39+C40+C41+C44</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="19">
-        <f>+C44+C35</f>
-        <v>1402097.4069999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="18"/>
+      <c r="C47" s="19">
+        <f>+C45+C36</f>
+        <v>2513442.1170000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="C49" s="159"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="C50" s="159"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="160" t="s">
-        <v>117</v>
-      </c>
-      <c r="B51" s="158"/>
-      <c r="C51" s="161">
-        <v>-135380.74219829985</v>
-      </c>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+    </row>
+    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="4"/>
+      <c r="C51" s="159"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="160" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B52" s="158"/>
-      <c r="C52" s="163">
-        <f>-(C35-C33)</f>
-        <v>-1402097.4069999999</v>
+      <c r="C52" s="161">
+        <v>-135380.74219829985</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="160" t="s">
+        <v>133</v>
+      </c>
+      <c r="B53" s="158"/>
+      <c r="C53" s="163">
+        <f>-(C36-C34)</f>
+        <v>-2513442.1170000001</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="B53" s="158"/>
-      <c r="C53" s="205">
+      <c r="B54" s="158"/>
+      <c r="C54" s="205">
         <f>'prorrateo '!F31</f>
         <v>2194116.7546521635</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="164"/>
-      <c r="C54" s="165"/>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="162" t="s">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="164"/>
+      <c r="C55" s="165"/>
+    </row>
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="157"/>
-      <c r="C55" s="166">
-        <f>SUM(C49:C53)</f>
-        <v>656638.60545386374</v>
-      </c>
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="9"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="10"/>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="219"/>
-      <c r="B57" s="219"/>
-      <c r="C57" s="219"/>
-      <c r="F57" s="44"/>
-    </row>
-    <row r="58" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="220"/>
-      <c r="B58" s="220"/>
-      <c r="C58" s="220"/>
-    </row>
-    <row r="59" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="26" t="s">
+      <c r="B56" s="157"/>
+      <c r="C56" s="166">
+        <f>SUM(C50:C54)</f>
+        <v>-454706.10454613669</v>
+      </c>
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="9"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="10"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="219"/>
+      <c r="B58" s="219"/>
+      <c r="C58" s="219"/>
+      <c r="F58" s="44"/>
+    </row>
+    <row r="59" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="220"/>
+      <c r="B59" s="220"/>
+      <c r="C59" s="220"/>
+    </row>
+    <row r="60" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B59" s="27"/>
-      <c r="C59" s="29"/>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="28" t="s">
+      <c r="B60" s="27"/>
+      <c r="C60" s="29"/>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="31">
-        <f>-C44</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="28"/>
       <c r="B61" s="28"/>
-      <c r="C61" s="31"/>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="31">
+        <f>-C45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="28"/>
       <c r="B62" s="28"/>
-      <c r="C62" s="32"/>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="167" t="s">
-        <v>0</v>
-      </c>
-      <c r="B63" s="168"/>
-      <c r="C63" s="169">
-        <f>SUM(C59:C62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="229" t="s">
-        <v>137</v>
-      </c>
-      <c r="B64" s="230"/>
-      <c r="C64" s="230"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="230"/>
-      <c r="B65" s="230"/>
-      <c r="C65" s="230"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="230"/>
-      <c r="B66" s="230"/>
-      <c r="C66" s="230"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
+      <c r="C62" s="31"/>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="28"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="32"/>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="167" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="168"/>
+      <c r="C64" s="169">
+        <f>SUM(C60:C63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="221" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" s="222"/>
+      <c r="C65" s="222"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="222"/>
+      <c r="B66" s="222"/>
+      <c r="C66" s="222"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="222"/>
+      <c r="B67" s="222"/>
+      <c r="C67" s="222"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A57:C58"/>
-    <mergeCell ref="A64:C66"/>
+    <mergeCell ref="A58:C59"/>
+    <mergeCell ref="A65:C67"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <hyperlinks>
@@ -2443,45 +2462,45 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="11"/>
+    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="221">
+      <c r="B1" s="223">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="221"/>
+      <c r="C1" s="223"/>
       <c r="D1" s="141">
         <v>1436145.71</v>
       </c>
       <c r="E1" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="223">
+      <c r="G1" s="225">
         <v>1000000</v>
       </c>
-      <c r="H1" s="223"/>
-    </row>
-    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="225"/>
+    </row>
+    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>27</v>
       </c>
@@ -2519,7 +2538,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
         <v>32</v>
       </c>
@@ -2561,7 +2580,7 @@
         <v>124487.04578100001</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>34</v>
       </c>
@@ -2603,7 +2622,7 @@
         <v>123999.816639</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>36</v>
       </c>
@@ -2645,7 +2664,7 @@
         <v>241472.783784</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="58" t="s">
         <v>39</v>
       </c>
@@ -2686,7 +2705,7 @@
       </c>
       <c r="O6" s="216"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>36</v>
       </c>
@@ -2729,7 +2748,7 @@
       </c>
       <c r="O7" s="216"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
         <v>42</v>
       </c>
@@ -2769,7 +2788,7 @@
         <v>123999.816639</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>44</v>
       </c>
@@ -2810,7 +2829,7 @@
       </c>
       <c r="O9" s="216"/>
     </row>
-    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="210" t="s">
         <v>46</v>
       </c>
@@ -2849,7 +2868,7 @@
         <v>769966.0654390722</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>112</v>
       </c>
@@ -2889,7 +2908,7 @@
         <v>122781.74378399999</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>49</v>
       </c>
@@ -2929,7 +2948,7 @@
         <v>126923.19149100001</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>51</v>
       </c>
@@ -2971,7 +2990,7 @@
         <v>124487.04578100001</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="184" t="s">
         <v>51</v>
       </c>
@@ -3010,7 +3029,7 @@
         <v>374456.40098510444</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>55</v>
       </c>
@@ -3049,7 +3068,7 @@
         <v>383275.49139613437</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="58" t="s">
         <v>58</v>
       </c>
@@ -3091,7 +3110,7 @@
         <v>126923.19149100001</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>61</v>
       </c>
@@ -3131,7 +3150,7 @@
         <v>122781.74378399999</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="62" t="s">
         <v>63</v>
       </c>
@@ -3171,7 +3190,7 @@
         <v>126923.19149100001</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>65</v>
       </c>
@@ -3211,7 +3230,7 @@
         <v>180274.78253999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.3">
       <c r="A20" s="184"/>
       <c r="B20" s="185" t="s">
         <v>116</v>
@@ -3250,7 +3269,7 @@
         <v>163371.97459218031</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="64"/>
       <c r="B21" s="59" t="s">
         <v>59</v>
@@ -3290,7 +3309,7 @@
         <v>26310.373668</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="142"/>
       <c r="B22" s="143"/>
       <c r="C22" s="144" t="s">
@@ -3327,7 +3346,7 @@
         <v>163371.97459218031</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="58"/>
       <c r="B23" s="59" t="s">
         <v>37</v>
@@ -3367,7 +3386,7 @@
         <v>48774.373668</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="58" t="s">
         <v>51</v>
       </c>
@@ -3409,7 +3428,7 @@
         <v>26310.373668</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>51</v>
       </c>
@@ -3446,7 +3465,7 @@
         <v>53673.162282719997</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="58" t="s">
         <v>65</v>
       </c>
@@ -3486,7 +3505,7 @@
         <v>26310.373668</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>65</v>
       </c>
@@ -3530,7 +3549,7 @@
         <v>232895.52987599999</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="68"/>
       <c r="B28" s="67" t="str">
         <f>B7</f>
@@ -3571,7 +3590,7 @@
         <v>26310.373668</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="68" t="s">
         <v>55</v>
       </c>
@@ -3610,7 +3629,7 @@
         <v>82130.462442028787</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="69"/>
       <c r="B30" s="69"/>
       <c r="C30" s="70"/>
@@ -3624,7 +3643,7 @@
       <c r="K30" s="73"/>
       <c r="L30" s="73"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="74"/>
       <c r="B31" s="75"/>
       <c r="C31" s="76" t="s">
@@ -3655,66 +3674,66 @@
         <v>4091523.4099954218</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="222"/>
-      <c r="B33" s="222"/>
-      <c r="C33" s="222"/>
-      <c r="D33" s="222"/>
-      <c r="E33" s="222"/>
-      <c r="F33" s="222"/>
-      <c r="G33" s="222"/>
-      <c r="H33" s="222"/>
-      <c r="I33" s="222"/>
-      <c r="J33" s="222"/>
-      <c r="K33" s="222"/>
-      <c r="L33" s="222"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="222"/>
-      <c r="B34" s="222"/>
-      <c r="C34" s="222"/>
-      <c r="D34" s="222"/>
-      <c r="E34" s="222"/>
-      <c r="F34" s="222"/>
-      <c r="G34" s="222"/>
-      <c r="H34" s="222"/>
-      <c r="I34" s="222"/>
-      <c r="J34" s="222"/>
-      <c r="K34" s="222"/>
-      <c r="L34" s="222"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="222"/>
-      <c r="B35" s="222"/>
-      <c r="C35" s="222"/>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="222"/>
-      <c r="G35" s="222"/>
-      <c r="H35" s="222"/>
-      <c r="I35" s="222"/>
-      <c r="J35" s="222"/>
-      <c r="K35" s="222"/>
-      <c r="L35" s="222"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="222"/>
-      <c r="B36" s="222"/>
-      <c r="C36" s="222"/>
-      <c r="D36" s="222"/>
-      <c r="E36" s="222"/>
-      <c r="F36" s="222"/>
-      <c r="G36" s="222"/>
-      <c r="H36" s="222"/>
-      <c r="I36" s="222"/>
-      <c r="J36" s="222"/>
-      <c r="K36" s="222"/>
-      <c r="L36" s="222"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="224"/>
+      <c r="B33" s="224"/>
+      <c r="C33" s="224"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="224"/>
+      <c r="F33" s="224"/>
+      <c r="G33" s="224"/>
+      <c r="H33" s="224"/>
+      <c r="I33" s="224"/>
+      <c r="J33" s="224"/>
+      <c r="K33" s="224"/>
+      <c r="L33" s="224"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="224"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="224"/>
+      <c r="J34" s="224"/>
+      <c r="K34" s="224"/>
+      <c r="L34" s="224"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="224"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="224"/>
+      <c r="J35" s="224"/>
+      <c r="K35" s="224"/>
+      <c r="L35" s="224"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="224"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="224"/>
+      <c r="J36" s="224"/>
+      <c r="K36" s="224"/>
+      <c r="L36" s="224"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3732,45 +3751,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="224" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="226" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="226"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="228"/>
       <c r="O1" s="78"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
       <c r="C2" s="173"/>
@@ -3788,7 +3807,7 @@
       <c r="O2" s="80"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="175"/>
@@ -3806,7 +3825,7 @@
       <c r="O3" s="80"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="82"/>
       <c r="B4" s="82"/>
       <c r="C4" s="175"/>
@@ -3826,7 +3845,7 @@
       <c r="O4" s="80"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="82"/>
       <c r="B5" s="82"/>
       <c r="C5" s="175"/>
@@ -3844,7 +3863,7 @@
       <c r="O5" s="80"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="82"/>
       <c r="B6" s="82"/>
       <c r="C6" s="173"/>
@@ -3862,13 +3881,13 @@
       <c r="O6" s="80"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="83"/>
       <c r="B7" s="83" t="s">
         <v>79</v>
       </c>
       <c r="C7" s="215">
-        <v>662901.94999999995</v>
+        <v>688312.66</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="173"/>
@@ -3880,7 +3899,7 @@
       <c r="I7" s="173"/>
       <c r="J7" s="173" t="str">
         <f>'detalle y gastos'!C7</f>
-        <v>Vto. 14/08</v>
+        <v>Vto. 15/09</v>
       </c>
       <c r="K7" s="173"/>
       <c r="L7" s="173"/>
@@ -3889,7 +3908,7 @@
       <c r="O7" s="80"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="83"/>
       <c r="B8" s="82" t="s">
         <v>79</v>
@@ -3905,16 +3924,16 @@
         <f>C8-J38</f>
         <v>-290631.84495</v>
       </c>
-      <c r="L8" s="228">
+      <c r="L8" s="230">
         <f>C7-J38</f>
-        <v>372270.10504999995</v>
-      </c>
-      <c r="M8" s="228"/>
+        <v>397680.81505000003</v>
+      </c>
+      <c r="M8" s="230"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
         <v>80</v>
       </c>
@@ -3959,7 +3978,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="100">
         <v>1</v>
       </c>
@@ -3999,7 +4018,7 @@
       </c>
       <c r="L10" s="129">
         <f>L$8*E10/S$12</f>
-        <v>19023.002368055</v>
+        <v>20321.489649055005</v>
       </c>
       <c r="M10" s="109">
         <f>G10-F10</f>
@@ -4007,15 +4026,15 @@
       </c>
       <c r="N10" s="106">
         <f>J10+L10</f>
-        <v>56800.40596805502</v>
+        <v>58098.893249055021</v>
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>181287.45174905504</v>
+        <v>182585.93903005501</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="101">
         <v>2</v>
       </c>
@@ -4055,7 +4074,7 @@
       </c>
       <c r="L11" s="129">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>18948.548347044998</v>
+        <v>20241.953486045</v>
       </c>
       <c r="M11" s="109">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
@@ -4063,15 +4082,15 @@
       </c>
       <c r="N11" s="106">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>50470.359047044993</v>
+        <v>51763.764186044995</v>
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>174470.175686045</v>
+        <v>175763.58082504501</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="100">
         <v>3</v>
       </c>
@@ -4111,7 +4130,7 @@
       </c>
       <c r="L12" s="129">
         <f t="shared" si="3"/>
-        <v>18762.41329452</v>
+        <v>20043.113078520004</v>
       </c>
       <c r="M12" s="109">
         <f>G12-F12</f>
@@ -4119,18 +4138,18 @@
       </c>
       <c r="N12" s="106">
         <f t="shared" si="5"/>
-        <v>21388.44929452</v>
+        <v>22669.149078520004</v>
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>262861.23307851999</v>
+        <v>264141.93286251999</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="100">
         <v>4</v>
       </c>
@@ -4170,7 +4189,7 @@
       </c>
       <c r="L13" s="129">
         <f t="shared" si="3"/>
-        <v>19395.272473104997</v>
+        <v>20719.170464105002</v>
       </c>
       <c r="M13" s="180">
         <f t="shared" si="4"/>
@@ -4178,15 +4197,15 @@
       </c>
       <c r="N13" s="106">
         <f t="shared" si="5"/>
-        <v>28586.398473104997</v>
+        <v>29910.296464105002</v>
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>155509.58996410499</v>
+        <v>156833.487955105</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="100">
         <v>6</v>
       </c>
@@ -4226,7 +4245,7 @@
       </c>
       <c r="L14" s="129">
         <f t="shared" si="3"/>
-        <v>19023.002368055</v>
+        <v>20321.489649055005</v>
       </c>
       <c r="M14" s="109">
         <f t="shared" si="4"/>
@@ -4234,15 +4253,15 @@
       </c>
       <c r="N14" s="106">
         <f t="shared" si="5"/>
-        <v>25972.619068054992</v>
+        <v>27271.106349054997</v>
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>150459.664849055</v>
+        <v>151758.15213005501</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="100">
         <v>7</v>
       </c>
@@ -4282,7 +4301,7 @@
       </c>
       <c r="L15" s="129">
         <f t="shared" si="3"/>
-        <v>18948.548347044998</v>
+        <v>20241.953486045</v>
       </c>
       <c r="M15" s="109">
         <f t="shared" si="4"/>
@@ -4290,14 +4309,14 @@
       </c>
       <c r="N15" s="106">
         <f t="shared" si="5"/>
-        <v>32547.663347045</v>
+        <v>33841.068486044998</v>
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>156547.47998604499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <v>157840.885125045</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="100">
         <v>8</v>
       </c>
@@ -4337,7 +4356,7 @@
       </c>
       <c r="L16" s="129">
         <f t="shared" si="3"/>
-        <v>19023.002368055</v>
+        <v>20321.489649055005</v>
       </c>
       <c r="M16" s="109">
         <f t="shared" si="4"/>
@@ -4345,14 +4364,14 @@
       </c>
       <c r="N16" s="106">
         <f t="shared" si="5"/>
-        <v>27388.802768054986</v>
+        <v>28687.290049054987</v>
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>151875.84854905499</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>153174.335830055</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="100">
         <v>9</v>
       </c>
@@ -4392,7 +4411,7 @@
       </c>
       <c r="L17" s="200">
         <f t="shared" si="3"/>
-        <v>18948.548347044998</v>
+        <v>20241.953486045</v>
       </c>
       <c r="M17" s="201">
         <f t="shared" si="4"/>
@@ -4400,14 +4419,14 @@
       </c>
       <c r="N17" s="196">
         <f t="shared" si="5"/>
-        <v>22371.773847044999</v>
+        <v>23665.178986045001</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>792337.83928611723</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>793631.24442511715</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="100">
         <v>10</v>
       </c>
@@ -4447,7 +4466,7 @@
       </c>
       <c r="L18" s="129">
         <f t="shared" si="3"/>
-        <v>18762.41329452</v>
+        <v>20043.113078520004</v>
       </c>
       <c r="M18" s="109">
         <f t="shared" si="4"/>
@@ -4455,14 +4474,14 @@
       </c>
       <c r="N18" s="106">
         <f t="shared" si="5"/>
-        <v>28094.219794520002</v>
+        <v>29374.919578520006</v>
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>150875.96357851999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152156.66336251999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="100">
         <v>11</v>
       </c>
@@ -4502,7 +4521,7 @@
       </c>
       <c r="L19" s="129">
         <f t="shared" si="3"/>
-        <v>19395.272473104997</v>
+        <v>20719.170464105002</v>
       </c>
       <c r="M19" s="109">
         <f>G19-F19</f>
@@ -4510,14 +4529,14 @@
       </c>
       <c r="N19" s="106">
         <f t="shared" si="5"/>
-        <v>49444.627273105012</v>
+        <v>50768.525264105017</v>
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>176367.81876410503</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177691.71675510501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="100">
         <v>12</v>
       </c>
@@ -4557,7 +4576,7 @@
       </c>
       <c r="L20" s="129">
         <f t="shared" si="3"/>
-        <v>19023.002368055</v>
+        <v>20321.489649055005</v>
       </c>
       <c r="M20" s="109">
         <f t="shared" si="4"/>
@@ -4565,14 +4584,14 @@
       </c>
       <c r="N20" s="106">
         <f t="shared" si="5"/>
-        <v>44504.930268054988</v>
+        <v>45803.41754905499</v>
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>168991.976049055</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>170290.463330055</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="100">
         <v>13</v>
       </c>
@@ -4612,7 +4631,7 @@
       </c>
       <c r="L21" s="200">
         <f t="shared" si="3"/>
-        <v>18948.548347044998</v>
+        <v>20241.953486045</v>
       </c>
       <c r="M21" s="201">
         <f t="shared" si="4"/>
@@ -4620,14 +4639,14 @@
       </c>
       <c r="N21" s="196">
         <f t="shared" si="5"/>
-        <v>44449.23364704501</v>
+        <v>45742.638786045012</v>
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>418905.63463214948</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>420199.03977114946</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="100">
         <v>14</v>
       </c>
@@ -4667,7 +4686,7 @@
       </c>
       <c r="L22" s="129">
         <f t="shared" si="3"/>
-        <v>18762.41329452</v>
+        <v>20043.113078520004</v>
       </c>
       <c r="M22" s="109">
         <f t="shared" si="4"/>
@@ -4675,14 +4694,14 @@
       </c>
       <c r="N22" s="106">
         <f t="shared" si="5"/>
-        <v>26663.968044519999</v>
+        <v>27944.667828520003</v>
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>409939.45944065438</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>411220.15922465437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="100">
         <v>15</v>
       </c>
@@ -4722,7 +4741,7 @@
       </c>
       <c r="L23" s="129">
         <f t="shared" si="3"/>
-        <v>19395.272473104997</v>
+        <v>20719.170464105002</v>
       </c>
       <c r="M23" s="109">
         <f t="shared" si="4"/>
@@ -4730,14 +4749,14 @@
       </c>
       <c r="N23" s="106">
         <f t="shared" si="5"/>
-        <v>34091.69537310498</v>
+        <v>35415.593364104985</v>
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>161014.88686410498</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>162338.78485510498</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="100">
         <v>16</v>
       </c>
@@ -4777,7 +4796,7 @@
       </c>
       <c r="L24" s="129">
         <f t="shared" si="3"/>
-        <v>18762.41329452</v>
+        <v>20043.113078520004</v>
       </c>
       <c r="M24" s="109">
         <f t="shared" si="4"/>
@@ -4785,14 +4804,14 @@
       </c>
       <c r="N24" s="106">
         <f t="shared" si="5"/>
-        <v>24520.935094519988</v>
+        <v>25801.634878519992</v>
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>147302.67887851998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>148583.37866251997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="100">
         <v>17</v>
       </c>
@@ -4832,7 +4851,7 @@
       </c>
       <c r="L25" s="129">
         <f t="shared" si="3"/>
-        <v>19395.272473104997</v>
+        <v>20719.170464105002</v>
       </c>
       <c r="M25" s="109">
         <f t="shared" si="4"/>
@@ -4840,14 +4859,14 @@
       </c>
       <c r="N25" s="106">
         <f t="shared" si="5"/>
-        <v>27414.060973104999</v>
+        <v>28737.958964105004</v>
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>154337.252464105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>155661.150455105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="100">
         <v>18</v>
       </c>
@@ -4887,7 +4906,7 @@
       </c>
       <c r="L26" s="129">
         <f t="shared" si="3"/>
-        <v>27547.987773699999</v>
+        <v>29428.380313700003</v>
       </c>
       <c r="M26" s="109">
         <f t="shared" si="4"/>
@@ -4895,14 +4914,14 @@
       </c>
       <c r="N26" s="106">
         <f>J26+L26</f>
-        <v>77986.636373700021</v>
+        <v>79867.028913700022</v>
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>258261.41891370001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>260141.81145370001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="100">
         <v>19</v>
       </c>
@@ -4932,21 +4951,21 @@
       <c r="K27" s="199"/>
       <c r="L27" s="200">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M27" s="201">
         <v>0</v>
       </c>
       <c r="N27" s="196">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>167392.4917267203</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>167666.92739472032</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="100">
         <v>20</v>
       </c>
@@ -4971,21 +4990,21 @@
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M28" s="109">
         <v>0</v>
       </c>
       <c r="N28" s="106">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>30330.890802540001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>30605.32647054</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
       <c r="C29" s="170" t="s">
@@ -5003,21 +5022,21 @@
       <c r="K29" s="151"/>
       <c r="L29" s="152">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M29" s="153">
         <v>0</v>
       </c>
       <c r="N29" s="150">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>167392.4917267203</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>167666.92739472032</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
       <c r="C30" s="181" t="s">
@@ -5035,21 +5054,21 @@
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M30" s="109">
         <v>0</v>
       </c>
       <c r="N30" s="106">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>52794.890802540001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>53069.32647054</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
       <c r="C31" s="181" t="s">
@@ -5067,21 +5086,21 @@
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M31" s="109">
         <v>0</v>
       </c>
       <c r="N31" s="106">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>30330.890802540001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>30605.32647054</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="100"/>
       <c r="B32" s="92"/>
       <c r="C32" s="132" t="s">
@@ -5099,21 +5118,21 @@
       <c r="K32" s="115"/>
       <c r="L32" s="129">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M32" s="109">
         <v>0</v>
       </c>
       <c r="N32" s="106">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>57693.679417259998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>57968.115085259997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="100"/>
       <c r="B33" s="92"/>
       <c r="C33" s="132" t="s">
@@ -5131,21 +5150,21 @@
       <c r="K33" s="115"/>
       <c r="L33" s="129">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M33" s="109">
         <v>0</v>
       </c>
       <c r="N33" s="106">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>30330.890802540001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>30605.32647054</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="100"/>
       <c r="B34" s="92"/>
       <c r="C34" s="132" t="s">
@@ -5163,21 +5182,21 @@
       <c r="K34" s="115"/>
       <c r="L34" s="129">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M34" s="109">
         <v>0</v>
       </c>
       <c r="N34" s="106">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>30330.890802540001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>30605.32647054</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="100">
         <v>21</v>
       </c>
@@ -5202,21 +5221,21 @@
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M35" s="109">
         <v>0</v>
       </c>
       <c r="N35" s="106">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>30330.890802540001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>30605.32647054</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="100">
         <v>22</v>
       </c>
@@ -5241,21 +5260,21 @@
       <c r="K36" s="108"/>
       <c r="L36" s="129">
         <f t="shared" si="3"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="M36" s="109">
         <v>0</v>
       </c>
       <c r="N36" s="106">
         <f t="shared" si="6"/>
-        <v>4020.5171345399995</v>
+        <v>4294.9528025400004</v>
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>86150.979576568789</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>86425.415244568794</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="100">
         <v>23</v>
       </c>
@@ -5285,7 +5304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="100">
         <v>24</v>
       </c>
@@ -5304,16 +5323,16 @@
       <c r="K38" s="115"/>
       <c r="L38" s="115">
         <f>SUM(L10:L37)</f>
-        <v>372270.10505000007</v>
+        <v>397680.8150499998</v>
       </c>
       <c r="M38" s="116"/>
       <c r="N38" s="112">
         <f>SUM(N10:N37)</f>
-        <v>662901.95000000019</v>
+        <v>688312.66000000038</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="80"/>
       <c r="C39" s="93"/>
       <c r="D39" s="94"/>
@@ -5332,47 +5351,47 @@
       <c r="K39" s="96"/>
       <c r="L39" s="135">
         <f>L38+J38</f>
-        <v>662901.95000000007</v>
+        <v>688312.6599999998</v>
       </c>
       <c r="M39" s="95"/>
       <c r="N39" s="95"/>
       <c r="O39" s="81"/>
     </row>
-    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="227"/>
-      <c r="D40" s="225"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
-      <c r="G40" s="225"/>
-      <c r="H40" s="225"/>
-      <c r="I40" s="225"/>
-      <c r="J40" s="225"/>
-      <c r="K40" s="225"/>
-      <c r="L40" s="225"/>
-      <c r="M40" s="225"/>
-      <c r="N40" s="225"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="227"/>
+      <c r="E40" s="227"/>
+      <c r="F40" s="227"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="227"/>
+      <c r="I40" s="227"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="227"/>
+      <c r="L40" s="227"/>
+      <c r="M40" s="227"/>
+      <c r="N40" s="227"/>
       <c r="O40" s="97"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H41" s="81"/>
       <c r="J41" s="98"/>
       <c r="K41" s="98"/>
       <c r="L41" s="98"/>
       <c r="N41" s="99"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L44" s="154"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L45" s="98"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E46" s="155"/>
       <c r="F46" s="155"/>
       <c r="G46" s="155"/>
